--- a/data/output/2025/evaluasi_71.xlsx
+++ b/data/output/2025/evaluasi_71.xlsx
@@ -22,6 +22,7 @@
     <sheet name="7171" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="7172" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="7173" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="7174" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -709,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -769,6 +770,314 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7108</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Siau Tagulandang Biaro</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.001426290470664</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7108</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Siau Tagulandang Biaro</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>55.62016191744008</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7108</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Siau Tagulandang Biaro</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7108</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Siau Tagulandang Biaro</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-11.82362041122243</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7108</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Siau Tagulandang Biaro</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7.637763737518013</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7108</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Siau Tagulandang Biaro</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6451803312451223</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7108</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Siau Tagulandang Biaro</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-4.638161959148809</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7108</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Siau Tagulandang Biaro</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.4318580382233838</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7108</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Siau Tagulandang Biaro</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5905491581925059</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7108</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Siau Tagulandang Biaro</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-2.116538962038295</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7108</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Siau Tagulandang Biaro</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.7577080157358205</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -783,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -871,6 +1180,314 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7109</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Tenggara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9769755545942129</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7109</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Tenggara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3.154028531300589</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7109</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Tenggara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>49.65948204060268</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7109</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Tenggara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7109</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Tenggara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-28.62456065463932</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7109</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Tenggara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.2550344911059406</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7109</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Tenggara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-10.42802753761963</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7109</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Tenggara</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1909311124835992</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7109</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Tenggara</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.788642988340052</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7109</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Tenggara</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.775235829433702</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7109</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Tenggara</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.071581175309924</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -885,7 +1502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -945,6 +1562,510 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7111</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Timur</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.285685522802068</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7111</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Timur</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2167891526300217</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7111</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Timur</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.008617291207283</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7111</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Timur</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>28.00726036840076</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7111</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Timur</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.382539520915157</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7111</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Timur</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7111</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Timur</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-69.01723515756841</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7111</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Timur</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8.967227700891076</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7111</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Timur</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.054027917549332</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7111</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Timur</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5680060012014768</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7111</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Timur</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-35.8131668576414</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7111</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Timur</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4.977926381497277</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7111</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Timur</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.01461215370841073</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7111</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Timur</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.1467866914253112</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7111</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Timur</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-4.348749271970987</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7111</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Timur</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-5.127579594025187</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7111</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Timur</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.02685994970565777</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7111</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Timur</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.2326656001023361</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -959,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1019,6 +2140,286 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7171</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Manado</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.461119601351874</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7171</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Manado</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>73.4568724201072</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7171</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Manado</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7171</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Manado</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-20.13098464031366</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7171</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Manado</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.506023943252017</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7171</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Manado</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-14.56024133005016</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7171</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Manado</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.7022415710979537</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7171</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Manado</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8702070727593449</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7171</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Manado</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.972947460737943</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7171</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Manado</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-1.474606881009825</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1033,7 +2434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1093,6 +2494,314 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7172</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Bitung</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1091537374656934</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7172</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Bitung</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>53.592871278001</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7172</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Bitung</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2208102048244145</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7172</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Bitung</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12.15651398110012</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7172</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Bitung</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7172</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Bitung</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8.705431452148449</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7172</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Bitung</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-1.595652647447087</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7172</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Bitung</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3.739400316651512</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7172</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Bitung</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>14.23366088461966</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7172</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Bitung</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>7.114505890891324</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7172</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Bitung</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.02531713252635237</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1107,7 +2816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1335,6 +3044,752 @@
       <c r="F8" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7173</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Tomohon</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3.543253839807207</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7173</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Tomohon</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.230424246259272</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7173</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Tomohon</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>8.003320160019751</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7173</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Tomohon</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7173</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Tomohon</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-9.475494163478146</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7173</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Tomohon</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.45250537087006</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7173</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kota Tomohon</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.1635109652178774</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7173</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kota Tomohon</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10.05850553883123</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7173</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kota Tomohon</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.14346513843021</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7173</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kota Tomohon</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.5918005746942401</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7173</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kota Tomohon</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.2138734293028806</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7173</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kota Tomohon</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.06432692256124566</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7174</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Kotamobagu</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.33599711438891</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7174</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Kotamobagu</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.509122851526253</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7174</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Kotamobagu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5.091516417007724</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7174</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Kotamobagu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11.66940119744918</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7174</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Kotamobagu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7174</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Kotamobagu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-5.223179659616347</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7174</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Kotamobagu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-12.82226337327121</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7174</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Kotamobagu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10.23604456688878</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7174</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Kotamobagu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.7481416932042805</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7174</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Kotamobagu</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-2.068686759357142</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7174</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Kotamobagu</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-8.163325812790868</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7174</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Kotamobagu</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.6617633374300572</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7174</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Kotamobagu</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.7844470388113445</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1349,7 +3804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1521,6 +3976,286 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7101</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.065829152133473</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7101</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.313403540951262</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7101</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.044083365175483</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7101</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10.76008546234423</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7101</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7101</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>7.552255089363119</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7101</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6.170881855147966</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7101</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.5759593497476913</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7101</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.7231451437247221</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7101</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.407572808673367</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1535,7 +4270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1763,6 +4498,258 @@
       <c r="F8" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7105</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Selatan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.607432837382951</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7105</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Selatan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7105</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Selatan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>8.741109269062509</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7105</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Selatan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>8.072214503594461</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7105</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Selatan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6.643402226366176</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7105</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Selatan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5.510242467506083</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7105</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Selatan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.5485859824621365</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7105</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Selatan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1.547388781431333</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7105</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Selatan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6.299034992554063</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q4-25_prov vs implisit_y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1777,7 +4764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1893,6 +4880,314 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7110</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Selatan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2.080387123210517</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7110</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Selatan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>6.634858967377499</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7110</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Selatan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-3.289218448243735</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7110</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Selatan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7110</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Selatan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-26.80578911490254</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7110</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Selatan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.350042199089499</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7110</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Selatan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-13.32952173399135</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7110</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Selatan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1138275265985579</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7110</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Selatan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.2018779402853539</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7110</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Selatan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.3917632405871267</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7110</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Selatan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.5003921046196071</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1907,7 +5202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1967,6 +5262,258 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7102</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3617402500229511</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7102</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.253753507940816</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7102</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7102</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7.727546356958996</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7102</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5.307178867940238</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7102</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.7236834150720474</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7102</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.2878526194588418</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7102</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-2.209542126368173</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7102</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.078459673631864</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1981,7 +5528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2041,6 +5588,314 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7103</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sangihe</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9167987040734581</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7103</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sangihe</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.429478473680102</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7103</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sangihe</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10.08210116239683</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7103</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sangihe</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>9.592749871555247</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7103</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sangihe</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7103</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sangihe</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.21650543385227</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7103</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sangihe</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6.197455470684116</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7103</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sangihe</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6.428228570741436</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7103</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sangihe</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4570077855060534</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7103</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sangihe</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5727533564928768</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7103</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sangihe</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.4572048408025459</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2055,7 +5910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2115,6 +5970,314 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7104</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Talaud</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.930160696935826</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7104</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Talaud</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.625041312171201</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7104</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Talaud</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3687859675800551</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7104</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Talaud</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>35.21354933697944</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7104</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Talaud</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7104</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Talaud</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6.866835927413358</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7104</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Talaud</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.72434264136063</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7104</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Talaud</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.595627411553425</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7104</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Talaud</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6.6522079822546</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7104</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Talaud</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.8702566022767059</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7104</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Talaud</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-2.727127538951933</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2129,7 +6292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2217,6 +6380,230 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7106</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.076610742415153</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7106</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2.22348853197829</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7106</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7106</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7.786087684336702</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7106</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6.224972584025642</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7106</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Utara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5.083891377372874</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7106</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Utara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.178659529917396</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7106</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Utara</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.157835838248336</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2231,7 +6618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2294,6 +6681,286 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7107</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3.057951637400306</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7107</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>28.20475232617277</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7107</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7107</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-18.68687124116585</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7107</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.351711019195092</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7107</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-9.897544113934572</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7107</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Utara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.09543557144300333</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7107</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Utara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.2837366111966356</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7107</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Utara</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.7383839890894898</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7107</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Utara</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.768691762283223</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
